--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -14,6 +14,8 @@
     <sheet name="5. Scale Costs" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. AI Deep Dive" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="7. Compliance + Econ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Security" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. Hire vs Outsource" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0&quot;/user&quot;"/>
@@ -30,8 +32,10 @@
     <numFmt numFmtId="168" formatCode="&quot;$&quot;0.000&quot;/credit&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="$#,##0"/>
+    <numFmt numFmtId="172" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -147,8 +151,43 @@
       <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -190,8 +229,13 @@
         <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -199,11 +243,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -255,6 +313,46 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -826,13 +924,167 @@
       </c>
     </row>
     <row r="21"/>
+    <row r="23">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>PRODUCT PRICING TIERS (Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Price / mo</t>
+        </is>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>Target segment</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>Assumed mix %</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>Blended contribution</t>
+        </is>
+      </c>
+      <c r="F24" s="48" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>Solo / Starter</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n">
+        <v>38</v>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>Sole trader / 1 client</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F25" s="49" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n">
+        <v>79</v>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>Bookkeeper w/ up to 5 clients</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E26" s="52" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="F26" s="49" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n">
+        <v>95</v>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>Firm w/ 10-30 clients</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E27" s="52" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F27" s="49" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n">
+        <v>149</v>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>Partner / 50+ clients / SSO</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="52" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F28" s="49" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>Blended ARPU</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="n">
+        <v>72</v>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>Used for revenue forecasts below</t>
+        </is>
+      </c>
+      <c r="D29" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="54" t="n">
+        <v>72</v>
+      </c>
+      <c r="F29" s="53" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>Assumed mix is intentionally conservative — early cohort tends to over-index on Standard + Pro; blended ARPU will land higher as Enterprise deals close.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F17"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A16:F17"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F21"/>
@@ -1499,7 +1751,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>REVENUE (assumes UK launch month 3, ARPU $35)</t>
+          <t>REVENUE (assumes UK launch month 3, blended ARPU $72)</t>
         </is>
       </c>
     </row>
@@ -1534,28 +1786,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MRR @ $35 ARPU</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>175</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1750</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H16" s="6">
+          <t>MRR @ blended $72 ARPU</t>
+        </is>
+      </c>
+      <c r="B16" s="57">
+        <f>B15*72.00</f>
+        <v/>
+      </c>
+      <c r="C16" s="57">
+        <f>C15*72.00</f>
+        <v/>
+      </c>
+      <c r="D16" s="57">
+        <f>D15*72.00</f>
+        <v/>
+      </c>
+      <c r="E16" s="57">
+        <f>E15*72.00</f>
+        <v/>
+      </c>
+      <c r="F16" s="57">
+        <f>F15*72.00</f>
+        <v/>
+      </c>
+      <c r="G16" s="57">
+        <f>G15*72.00</f>
+        <v/>
+      </c>
+      <c r="H16" s="57">
         <f>SUM(B16:G16)</f>
         <v/>
       </c>
@@ -3423,8 +3681,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -3826,81 +4084,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARPU @ break-even (2x)</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>17</v>
+          <t>ARPU @ blended tier mix ($72)</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="n">
+        <v>72</v>
+      </c>
+      <c r="C28" s="58" t="n">
+        <v>72</v>
+      </c>
+      <c r="D28" s="58" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARPU @ healthy (4x)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>34</v>
+          <t>ARPU @ Enterprise-heavy mix ($95)</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="C29" s="57" t="n">
+        <v>95</v>
+      </c>
+      <c r="D29" s="57" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MRR @ 4x ARPU</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>44000</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>103000</v>
+          <t>MRR @ blended $72 ARPU</t>
+        </is>
+      </c>
+      <c r="B30" s="57">
+        <f>500*72.00</f>
+        <v/>
+      </c>
+      <c r="C30" s="57">
+        <f>1500*72.00</f>
+        <v/>
+      </c>
+      <c r="D30" s="57">
+        <f>3000*72.00</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross margin @ $35 ARPU</t>
+          <t>Gross margin @ blended $72 ARPU</t>
         </is>
       </c>
       <c r="B31" s="44" t="n">
-        <v>0.77</v>
+        <v>0.889</v>
       </c>
       <c r="C31" s="44" t="n">
-        <v>0.79</v>
+        <v>0.899</v>
       </c>
       <c r="D31" s="44" t="n">
-        <v>0.75</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross margin @ $50 ARPU</t>
+          <t>Gross margin @ $95 ARPU (Pro heavy)</t>
         </is>
       </c>
       <c r="B32" s="44" t="n">
-        <v>0.84</v>
+        <v>0.916</v>
       </c>
       <c r="C32" s="44" t="n">
-        <v>0.85</v>
+        <v>0.923</v>
       </c>
       <c r="D32" s="44" t="n">
-        <v>0.83</v>
+        <v>0.909</v>
       </c>
     </row>
   </sheetData>
@@ -3912,4 +4173,2137 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>Operational Security — Line-Item Costs by User Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="56" t="inlineStr">
+        <is>
+          <t>Ship what a real accounting SaaS needs. Bank data + PII means security is not optional. Numbers are $/mo unless noted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>Pre-launch</t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>500 low</t>
+        </is>
+      </c>
+      <c r="E4" s="48" t="inlineStr">
+        <is>
+          <t>500 high</t>
+        </is>
+      </c>
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>1,500 low</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="inlineStr">
+        <is>
+          <t>1,500 high</t>
+        </is>
+      </c>
+      <c r="H4" s="48" t="inlineStr">
+        <is>
+          <t>3,000+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Perimeter</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr"/>
+      <c r="C5" s="60" t="inlineStr"/>
+      <c r="D5" s="60" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
+      <c r="F5" s="60" t="inlineStr"/>
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr"/>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>Cloudflare WAF + DDoS + Bot Mgmt</t>
+        </is>
+      </c>
+      <c r="C6" s="50" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="50" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr"/>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>Cloudflare Zero Trust (team VPN)</t>
+        </is>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="50" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>Secrets Mgmt</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr"/>
+      <c r="C8" s="60" t="inlineStr"/>
+      <c r="D8" s="60" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
+      <c r="F8" s="60" t="inlineStr"/>
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr"/>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>Doppler / Infisical (env + rotation)</t>
+        </is>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" s="50" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr"/>
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>AWS/Google Secret Manager (per-svc keys)</t>
+        </is>
+      </c>
+      <c r="C10" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="50" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="inlineStr">
+        <is>
+          <t>SSO / IAM</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="inlineStr"/>
+      <c r="C11" s="60" t="inlineStr"/>
+      <c r="D11" s="60" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
+      <c r="F11" s="60" t="inlineStr"/>
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr"/>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>SSO (SAML/OIDC) for Enterprise plan</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50" t="n">
+        <v>250</v>
+      </c>
+      <c r="H12" s="50" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>1Password Business (per seat, team of 6)</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>48</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>48</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" s="50" t="n">
+        <v>96</v>
+      </c>
+      <c r="G13" s="50" t="n">
+        <v>96</v>
+      </c>
+      <c r="H13" s="50" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr"/>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>MFA enforcement (Auth0/WorkOS add-on)</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="G14" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" s="50" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>App Security</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="inlineStr"/>
+      <c r="C15" s="60" t="inlineStr"/>
+      <c r="D15" s="60" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr"/>
+      <c r="F15" s="60" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr"/>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>Snyk / Semgrep (SAST + dep scanning)</t>
+        </is>
+      </c>
+      <c r="C16" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" s="50" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr"/>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>GitHub Advanced Security</t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="F17" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" s="50" t="n">
+        <v>147</v>
+      </c>
+      <c r="H17" s="50" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr"/>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>DAST (StackHawk / Detectify weekly scan)</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="50" t="n">
+        <v>250</v>
+      </c>
+      <c r="G18" s="50" t="n">
+        <v>400</v>
+      </c>
+      <c r="H18" s="50" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>Bug Bounty</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="inlineStr"/>
+      <c r="C19" s="60" t="inlineStr"/>
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr"/>
+      <c r="F19" s="60" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr"/>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>HackerOne / Intigriti public program</t>
+        </is>
+      </c>
+      <c r="C20" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="G20" s="50" t="n">
+        <v>800</v>
+      </c>
+      <c r="H20" s="50" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr"/>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>Bounty pool (avg payouts, budgeted)</t>
+        </is>
+      </c>
+      <c r="C21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="50" t="n">
+        <v>600</v>
+      </c>
+      <c r="H21" s="50" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr"/>
+      <c r="C22" s="60" t="inlineStr"/>
+      <c r="D22" s="60" t="inlineStr"/>
+      <c r="E22" s="60" t="inlineStr"/>
+      <c r="F22" s="60" t="inlineStr"/>
+      <c r="G22" s="60" t="inlineStr"/>
+      <c r="H22" s="60" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr"/>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>MDM (Kandji/Jamf, per device)</t>
+        </is>
+      </c>
+      <c r="C23" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="50" t="n">
+        <v>180</v>
+      </c>
+      <c r="G23" s="50" t="n">
+        <v>240</v>
+      </c>
+      <c r="H23" s="50" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr"/>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>EDR (CrowdStrike/SentinelOne, per seat)</t>
+        </is>
+      </c>
+      <c r="C24" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="50" t="n">
+        <v>36</v>
+      </c>
+      <c r="E24" s="50" t="n">
+        <v>36</v>
+      </c>
+      <c r="F24" s="50" t="n">
+        <v>108</v>
+      </c>
+      <c r="G24" s="50" t="n">
+        <v>144</v>
+      </c>
+      <c r="H24" s="50" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>Logging &amp; Alerts</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr"/>
+      <c r="C25" s="60" t="inlineStr"/>
+      <c r="D25" s="60" t="inlineStr"/>
+      <c r="E25" s="60" t="inlineStr"/>
+      <c r="F25" s="60" t="inlineStr"/>
+      <c r="G25" s="60" t="inlineStr"/>
+      <c r="H25" s="60" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr"/>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>SIEM (Panther / Datadog Cloud SIEM)</t>
+        </is>
+      </c>
+      <c r="C26" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="G26" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="H26" s="50" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr"/>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>Audit-log retention (S3 Glacier)</t>
+        </is>
+      </c>
+      <c r="C27" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="H27" s="50" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>Backup / DR</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="inlineStr"/>
+      <c r="C28" s="60" t="inlineStr"/>
+      <c r="D28" s="60" t="inlineStr"/>
+      <c r="E28" s="60" t="inlineStr"/>
+      <c r="F28" s="60" t="inlineStr"/>
+      <c r="G28" s="60" t="inlineStr"/>
+      <c r="H28" s="60" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr"/>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>Cross-region MongoDB backup + PITR</t>
+        </is>
+      </c>
+      <c r="C29" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="G29" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" s="50" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr"/>
+      <c r="B30" s="49" t="inlineStr">
+        <is>
+          <t>Immutable off-site backup (Wasabi/S3 lock)</t>
+        </is>
+      </c>
+      <c r="C30" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="F30" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="H30" s="50" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="60" t="inlineStr">
+        <is>
+          <t>Compliance Ops</t>
+        </is>
+      </c>
+      <c r="B31" s="60" t="inlineStr"/>
+      <c r="C31" s="60" t="inlineStr"/>
+      <c r="D31" s="60" t="inlineStr"/>
+      <c r="E31" s="60" t="inlineStr"/>
+      <c r="F31" s="60" t="inlineStr"/>
+      <c r="G31" s="60" t="inlineStr"/>
+      <c r="H31" s="60" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr"/>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>Vanta / Drata (SOC 2 automation)</t>
+        </is>
+      </c>
+      <c r="C32" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="50" t="n">
+        <v>800</v>
+      </c>
+      <c r="G32" s="50" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H32" s="50" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr"/>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>Annual pen-test (amortised /mo)</t>
+        </is>
+      </c>
+      <c r="C33" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>750</v>
+      </c>
+      <c r="H33" s="50" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr"/>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>IR retainer (Kroll / Mandiant)</t>
+        </is>
+      </c>
+      <c r="C34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="50" t="n">
+        <v>400</v>
+      </c>
+      <c r="H34" s="50" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Fraud / Abuse</t>
+        </is>
+      </c>
+      <c r="B35" s="60" t="inlineStr"/>
+      <c r="C35" s="60" t="inlineStr"/>
+      <c r="D35" s="60" t="inlineStr"/>
+      <c r="E35" s="60" t="inlineStr"/>
+      <c r="F35" s="60" t="inlineStr"/>
+      <c r="G35" s="60" t="inlineStr"/>
+      <c r="H35" s="60" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr"/>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>reCAPTCHA Enterprise + IP intel</t>
+        </is>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="G36" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Rate-limit + abuse mgmt (Kong/Cloudflare)</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="F37" s="50" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="H37" s="50" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="61" t="inlineStr">
+        <is>
+          <t>TOTAL SECURITY / MONTH</t>
+        </is>
+      </c>
+      <c r="B39" s="62" t="n"/>
+      <c r="C39" s="63">
+        <f>SUM(C5:C37)</f>
+        <v/>
+      </c>
+      <c r="D39" s="63">
+        <f>SUM(D5:D37)</f>
+        <v/>
+      </c>
+      <c r="E39" s="63">
+        <f>SUM(E5:E37)</f>
+        <v/>
+      </c>
+      <c r="F39" s="63">
+        <f>SUM(F5:F37)</f>
+        <v/>
+      </c>
+      <c r="G39" s="63">
+        <f>SUM(G5:G37)</f>
+        <v/>
+      </c>
+      <c r="H39" s="63">
+        <f>SUM(H5:H37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="47" t="inlineStr">
+        <is>
+          <t>Notes &amp; phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
+        <is>
+          <t>• Pre-launch = what you must have on Day 1 (Cloudflare, secrets, MFA, 1Password, encrypted backups).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
+        <is>
+          <t>• 500-user tier = layer in Snyk, MDM, EDR, basic SIEM. This is the SOC-2 Type I readiness moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr">
+        <is>
+          <t>• 1,500-user tier = SOC 2 automation (Vanta), pen-test, DAST, bug bounty program launches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="64" t="inlineStr">
+        <is>
+          <t>• 3,000+ = mature program — SIEM w/ retention, IR retainer, GitHub Advanced Security, dedicated fraud tooling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="64" t="inlineStr">
+        <is>
+          <t>• Numbers exclude Vanta itself in the 500 column (still in Compliance + Econ tab); avoid double-counting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="64" t="inlineStr">
+        <is>
+          <t>• All prices are conservative-mid list; real spend often 10-20% lower after annual commits.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>Hire vs Outsource — What we build vs. what we contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="56" t="inlineStr">
+        <is>
+          <t>Reality check: 2-founder team + Emergent dev credits. This tab shows what's genuinely covered by that setup, what should be outsourced now (fractional / contract), and when a full-time hire becomes necessary — with the revenue or user trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t>A. What the current team (2 founders + Emergent) handles</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Owner today</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>Risk if we stay solo</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>Backup plan</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>Backend + API dev</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>You + Emergent</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>Full feature build; hot-reload FastAPI + Mongo</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>Bus factor of 1</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>Emergent contract dev on retainer</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>Emergent dev credits cover surges</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>Frontend (React)</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>You + Emergent</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>React + Tailwind + shadcn</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>UI polish behind roadmap</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>Fractional design contractor</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>Design system already in place</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>Product management</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>Roadmap, feature spec, user research</t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>You become the bottleneck</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>Hire PM at ~1,500 users</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="inlineStr">
+        <is>
+          <t>You know the accounting domain cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>Basic DevOps</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>You + Emergent</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>Railway + Atlas + supervisor</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>3am pager on outages</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>Ops-as-service (Cloudops)</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>Managed platform absorbs most work</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>QA — smoke + unit</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>You + subagents</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>pytest + testing-agent</t>
+        </is>
+      </c>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>Coverage gaps around edge cases</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>Contract QA at 750 users</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>Test agents good, human QA still needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>Sales — founder-led</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>Direct outbound to first 100 accountants</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>Doesn't scale past ~250 clients</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>Hire sales lead at $30k MRR</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="inlineStr">
+        <is>
+          <t>Best channel until Series A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>Content + copywriting</t>
+        </is>
+      </c>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>You + LLM</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>Blog, pitch decks, docs</t>
+        </is>
+      </c>
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>Voice / brand consistency</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>Fractional content writer</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
+        <is>
+          <t>LLM does 80%; human editor for polish</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>Bookkeeping (of SmartBooks)</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>Ironically, you can do your own books</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="inlineStr">
+        <is>
+          <t>Time drain when scaling</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>Outsource at Series A</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
+        <is>
+          <t>Eat your own dogfood</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>B. Outsource / contract NOW (fractional, not full-time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>Provider type</t>
+        </is>
+      </c>
+      <c r="C17" s="48" t="inlineStr">
+        <is>
+          <t>Why outsource</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>Cost range ($/mo)</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>When to start</t>
+        </is>
+      </c>
+      <c r="F17" s="48" t="inlineStr">
+        <is>
+          <t>Full-time trigger</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>Legal / TOS + Privacy</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Startup law firm (Cooley / Gunderson) or LegalZoom+lawyer review</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>Bank data + PII = real regulatory exposure</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="inlineStr">
+        <is>
+          <t>$500–$1,500 flat / project</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>General Counsel @ $8M ARR</t>
+        </is>
+      </c>
+      <c r="G18" s="49" t="inlineStr">
+        <is>
+          <t>One-time TOS + Privacy $3–5k, then retainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>Accounting / Tax (yours)</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>Fractional accountant / bookkeeper</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>You're building an accounting product — filing DE + UK taxes wrong is a bad look</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>$300–$800</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t>In-house CFO @ $2M ARR</t>
+        </is>
+      </c>
+      <c r="G19" s="49" t="inlineStr">
+        <is>
+          <t>Especially UK VAT + HMRC filings</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>Compliance / SOC 2</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>Vanta + independent auditor</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>You can't self-attest — auditor must be external</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>$800–$1,500</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>1,000 users</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>Full-time Compliance @ 5,000 users</t>
+        </is>
+      </c>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>Vanta handles evidence; auditor signs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>Design (brand + product)</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>Fractional designer / studio</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Founders can ship UI but marketing site + brand consistency needs a designer</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="inlineStr">
+        <is>
+          <t>$1,500–$4,000</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>Pre-launch marketing site</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>Full-time Designer @ 2,000 users</t>
+        </is>
+      </c>
+      <c r="G21" s="49" t="inlineStr">
+        <is>
+          <t>Especially for pitch decks + demos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>Cybersecurity audit</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t>Boutique pen-test firm (Bishop Fox, Cure53)</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>You can't SOC 2 without an external pen-test</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="inlineStr">
+        <is>
+          <t>$500–$1,000 (amortised)</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>1,500 users</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>In-house Security Eng @ 5,000 users</t>
+        </is>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>Annual test = $6–12k one-shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>Customer support / SDR</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>Fractional VA / offshore SDR</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Save founder time on demos, scheduling, tier-1 questions</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>$800–$2,500</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>First paid signups</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>In-house CS @ $20k MRR</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>Time zone bonus for UK coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>Marketing / SEO / paid</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>Fractional CMO or agency</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>You need SEO from Day 1 but shouldn't hire full-time yet</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>$2,000–$5,000</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>Post-launch</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>Head of Growth @ $50k MRR</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>Content-led compounds slowly, start early</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>Payroll / HR</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>Gusto / Deel / Rippling</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>SaaS handles this; DIY is a mistake past 3 people</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>$40–$120 + $10/employee</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>First hire</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>HR person @ 20+ headcount</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>Deel if hiring UK/EU contractors</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>Recruiting</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>Contingent recruiter</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>Only pay on hire; save you weeks of screening</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>15–20% first-year salary /hire</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>Second hire</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>In-house recruiter @ 25+ headcount</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>Skip for junior hires — use LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="inlineStr">
+        <is>
+          <t>C. Full-time hires — role, US mid salary, and trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Hire order</t>
+        </is>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>Base salary ($k)</t>
+        </is>
+      </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>Loaded cost ($k/yr)</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="F30" s="48" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="G30" s="48" t="inlineStr">
+        <is>
+          <t>Alt: keep fractional?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Eng #1</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>1st hire</t>
+        </is>
+      </c>
+      <c r="C31" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="D31" s="50" t="n">
+        <v>195</v>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>$25k MRR OR launch of UK</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>Second builder to remove bus factor + accelerate roadmap</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>No — need permanent code owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>Customer Success Lead</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>2nd hire</t>
+        </is>
+      </c>
+      <c r="C32" s="50" t="n">
+        <v>75</v>
+      </c>
+      <c r="D32" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>$40k MRR (~1,000 paid users)</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>Onboarding + retention on autopilot</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>Fractional VA until $20k MRR, then must hire</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>Head of Growth / Marketing</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>3rd hire</t>
+        </is>
+      </c>
+      <c r="C33" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>170</v>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>$60k MRR</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>Move from founder-led to demand-gen engine</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="inlineStr">
+        <is>
+          <t>Yes — fractional CMO can run to $100k MRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Eng #2</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>4th hire</t>
+        </is>
+      </c>
+      <c r="C34" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="D34" s="50" t="n">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>1,500 users OR $60k MRR</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>Split frontend / backend ownership; on-call rotation</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>No — need full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t>Head of Sales / AE</t>
+        </is>
+      </c>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>5th hire</t>
+        </is>
+      </c>
+      <c r="C35" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="D35" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>$80k MRR + $150k+ ACVs</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>Enterprise/Partner tier deals need dedicated closer</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t>Yes — fractional sales advisor until then</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>DevOps / Platform Eng</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>6th hire</t>
+        </is>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>210</v>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>2,000 users OR SOC 2 Type II</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>Uptime, SRE, IaC — bank-data SaaS needs this</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>Fractional Cloudops fine to ~1,500 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>Compliance Lead</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>7th hire</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="D37" s="50" t="n">
+        <v>170</v>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>SOC 2 Type II + ISO 27001 push</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t>Full-time evidence + vendor mgmt + audit prep</t>
+        </is>
+      </c>
+      <c r="G37" s="49" t="inlineStr">
+        <is>
+          <t>Vanta + fractional to 5,000 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>Design Lead</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>8th hire</t>
+        </is>
+      </c>
+      <c r="C38" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="D38" s="50" t="n">
+        <v>170</v>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>2,000 users</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>Product design consistency; brand ownership</t>
+        </is>
+      </c>
+      <c r="G38" s="49" t="inlineStr">
+        <is>
+          <t>Fractional works longer than most think</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>Data / Analytics Eng</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>9th hire</t>
+        </is>
+      </c>
+      <c r="C39" s="50" t="n">
+        <v>145</v>
+      </c>
+      <c r="D39" s="50" t="n">
+        <v>190</v>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>3,000 users</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t>Feature analytics, ML on categorisation, customer insights</t>
+        </is>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>Contract data analyst can bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>General Counsel</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr">
+        <is>
+          <t>10th hire</t>
+        </is>
+      </c>
+      <c r="C40" s="50" t="n">
+        <v>175</v>
+      </c>
+      <c r="D40" s="50" t="n">
+        <v>225</v>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>$8M ARR</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>Contracts, IP, partnerships, disputes</t>
+        </is>
+      </c>
+      <c r="G40" s="49" t="inlineStr">
+        <is>
+          <t>Yes — outside counsel scales far</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>Head of Finance / CFO</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>11th hire</t>
+        </is>
+      </c>
+      <c r="C41" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="D41" s="50" t="n">
+        <v>260</v>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>Series A or $5M ARR</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>Board reporting, forecasting, fundraising, taxes</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>Fractional CFO to Series A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="47" t="inlineStr">
+        <is>
+          <t>D. Rules of thumb</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="64" t="inlineStr">
+        <is>
+          <t>• Loaded cost ≈ base × 1.3 (US) or × 1.15 (UK/EU contractor via Deel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="64" t="inlineStr">
+        <is>
+          <t>• Never hire full-time for something you can't keep busy 60%+ of the week — use fractional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="64" t="inlineStr">
+        <is>
+          <t>• First 5 hires shape company culture; over-index on hiring signal, under-index on comp comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr">
+        <is>
+          <t>• Every role above has a fractional or contract alternative — always try that first for one quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t>• Rule of engineering headcount: 1 engineer per ~$500k–$1M ARR in accounting SaaS (higher because of compliance overhead).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="64" t="inlineStr">
+        <is>
+          <t>• Rule for Bay Area vs. remote-first: Remote-first saves ~25% on comp with similar quality if you interview well.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -15,6 +15,7 @@
     <sheet name="6. AI Deep Dive" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="7. Security" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="8. Profit Breakdown" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. Hire Timeline" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5165,30 +5166,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profit Breakdown — using $38 / $75 / $95 / $149 tiers</t>
+          <t>Profit Breakdown — infra-only vs. ALL-IN (with team)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blended ARPU = $70.60 (mix: 40% Solo / 35% Standard / 15% Pro / 10% Enterprise). Tech costs from the Scale Costs tab.</t>
+          <t>Blended ARPU = $70.60 (40/35/15/10 mix of $38/$75/$95/$149). All-in adds outsource + FTE loaded costs.</t>
         </is>
       </c>
     </row>
@@ -5236,6 +5238,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -5260,6 +5263,7 @@
         <v>84720</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -5284,6 +5288,7 @@
         <v>211800</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -5308,6 +5313,7 @@
         <v>423600</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -5332,6 +5338,7 @@
         <v>847200</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -5356,6 +5363,7 @@
         <v>1270800</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -5380,6 +5388,7 @@
         <v>2541600</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -5404,18 +5413,19 @@
         <v>4236000</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>B. Gross profit at blended $70.60 ARPU</t>
+          <t>B. INFRA-ONLY gross profit — the unit-economics number</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Total users</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -5425,12 +5435,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Tech COGS /mo</t>
+          <t>Infra + SaaS + AI</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Gross profit /mo</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -5449,6 +5459,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -5473,6 +5484,7 @@
         <v>35</v>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -5497,6 +5509,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -5521,6 +5534,7 @@
         <v>8</v>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -5545,6 +5559,7 @@
         <v>8.5</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -5569,6 +5584,7 @@
         <v>7.333333333333333</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -5593,6 +5609,7 @@
         <v>8.666666666666666</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -5617,319 +5634,1543 @@
         <v>8.4</v>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>C. Break-even user count by cost scenario</t>
+          <t>C. ALL-IN monthly cost + margin (infra + outsource + FTE loaded)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>FTE loaded</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>All-in cost</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>All-in profit</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>All-in margin</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>7060.000000000001</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>560.0000000000009</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0.07932011331444772</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>6720.000000000011</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>17650</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>9650.000000000004</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0.5467422096317281</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>115800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>35300.00000000001</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>25300.00000000001</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0.7167138810198301</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>303600.0000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>70600.00000000001</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>16250</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>31750</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>38850.00000000001</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0.5502832861189803</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>466200.0000000002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>53750</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>52150.00000000001</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>0.4924457034938622</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>625800.0000000002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>211800</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>82083.33333333333</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>118083.3333333333</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>93716.6666666667</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0.4424771797293044</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1124600</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>353000.0000000001</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>82083.33333333333</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>132083.3333333333</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>220916.6666666667</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0.625826251180359</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>2651000.000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>D. Break-even users by cost scenario (blended $70.60 ARPU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Tech burn /mo</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Break-even users @ $71 blended</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Break-even @ $75 (Standard)</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Break-even @ $95 (Pro)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Total burn /mo</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Break-even @ blended</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>@ $75 Std</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>@ $95 Pro</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Bare-minimum floor (paused build)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Steady state (1 fractional dev)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Pre-launch today (heavy build)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>220</v>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>207</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>163</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Post-launch, no FTE (500u infra + outs)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>142</v>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>133</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>105</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>1 FTE hired (1,000u stage)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>31750</v>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>450</v>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>423</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>334</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Full core team (3,000u stage)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>86083</v>
+      </c>
+      <c r="C44" s="25" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>906</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>E. Blended-ARPU sensitivity by tier mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Mix scenario</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Solo %</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Standard %</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Pro %</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Ent %</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Blended ARPU</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>MRR @ 1,500u</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Solo-heavy (Freemium bleed)</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>83820</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Baseline (current plan)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>70.60000000000001</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise-tilted</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>136650</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise-heavy (Partners)</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>154800</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Takeaway: infra-only margin stays ~87-89% through the whole ramp. All-in margin dips to ~49% at 1,500u (post-Platform-Eng hire) and ~44% at 3,000u as the core team fills out, then rebounds to ~63% at 5,000u once revenue outpaces headcount. This is the classic SaaS S-curve — the pitch is: infra margin proves the model, all-in margin proves you can operate it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A26:I26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Outsource &amp; Hire Timeline — what, when, why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological plan tied to user milestones. Each row shows the trigger (users or MRR), monthly cost impact, cumulative team spend, and the MRR available at that point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. IMMEDIATE — active or start within 30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Users at trigger</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MRR at trigger</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Emergent contract dev (current)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Active today</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Extra hands during heavy build; scales up to $8k/mo as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Fractional QA engineer</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Post-launch</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3530</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Playwright smoke suite once users hit the app</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity vendor SaaS (Snyk, Doppler, Cloudflare Zero Trust)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Not a person — set up before first paying user</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>B. GROWTH STAGE — 250 to 1,500 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Users at trigger</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>MRR at trigger</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Fractional Platform / DevOps engineer</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1,000 users</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>70600</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>SRE, IaC, cost tuning; keep until Platform FTE hired</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Sr Full-Stack Eng #1 (FTE)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>16250</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>$25k MRR OR UK launch</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>355</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>25063</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Second permanent code owner — kills bus factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Fractional Security engineer</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>SOC 2 kickoff / 1,000 users</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>70600</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Threat model, IAM review, SIEM tuning, IR playbooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Annual pen-test (amortised)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>SOC 2 Type I readiness (1,500u)</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>$6-12k one-shot; required for SOC 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>HackerOne / Intigriti bug bounty program</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1,500 users</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Platform fee + budgeted bounty pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Platform / DevOps Eng (FTE)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>17500</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1,500 users OR SOC 2 Type II</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Convert fractional to FTE; on-call ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>C. SCALE STAGE — 1,500 to 5,000 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Users at trigger</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>MRR at trigger</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Fractional Data / Analytics engineer</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>1,500 users</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Feature analytics, categorisation ML, churn model</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Fractional Product Designer</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Marketing site + brand refresh</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>70600</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Design system + marketing site + pitch materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Incident Response retainer (Kroll / Mandiant)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>1,500 users</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Pre-paid breach response hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Sr Full-Stack Eng #2 (FTE)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>16250</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>3,000 users OR $60k MRR</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>850</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>60010</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Split frontend/backend; on-call rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Security Engineer (FTE)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>18333</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>SOC 2 Type II + first enterprise deal</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>211800</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Full-time threat model, IR ownership, SSO reviews</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Bare-minimum floor (paused build)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C28" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="D28" s="25" t="n">
-        <v>28</v>
+          <t>QA / Test Automation Lead (FTE)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>13750</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>3,000 users</t>
+        </is>
       </c>
       <c r="E28" s="25" t="n">
-        <v>22</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Steady state (1 fractional dev)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>78</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>73</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>58</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Current heavy-build burn</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>15500</v>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>220</v>
-      </c>
-      <c r="D30" s="25" t="n">
-        <v>207</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>163</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>211800</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Convert fractional QA; Playwright + performance suites</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Post-launch @ 500-user infra</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D. Cumulative team cost at each milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Outsource /mo</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FTEs on payroll</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FTE /mo</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Team total /mo</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>MRR at milestone</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Team % of MRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>100 users</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>7060.000000000001</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.4249291784702549</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>250 users</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="C31" s="25" t="n">
-        <v>57</v>
-      </c>
-      <c r="D31" s="25" t="n">
-        <v>53</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>42</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Post-launch @ 1,500-user infra</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>11000</v>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>156</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>147</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>116</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>17650</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.2266288951841359</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>D. Blended-ARPU sensitivity by tier mix</t>
-        </is>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>500 users</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>35300.00000000001</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.169971671388102</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Mix scenario</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Solo %</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Standard %</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Pro %</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Ent %</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Blended ARPU</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>MRR @ 1,500 users</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>1000 users</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Sr SWE #1</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>16250</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>23250</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>70600.00000000001</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.3293201133144475</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Solo-heavy (Freemium bleed)</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>83820</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>1500 users</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Sr SWE #1, Platform Eng</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>33750</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>42750</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>105900</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.4036827195467422</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Baseline (current plan)</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>70.60000000000001</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>105900</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>3000 users</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Sr SWE #1, Sr SWE #2, Platform Eng, Security Eng, QA Lead</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>82083.33333333333</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>92083.33333333333</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>211800</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.4347655020459552</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Enterprise-tilted</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>136650</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Enterprise-heavy (Partners)</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>154800</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
+          <t>5000 users</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Sr SWE #1, Sr SWE #2, Platform Eng, Security Eng, QA Lead</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>82083.33333333333</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>90083.33333333333</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>353000.0000000001</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.2551935788479697</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>E. Decision rules</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>Takeaway: at 1,500 users on the baseline mix, MRR ~$106k against ~$11k/mo tech cost = ~90% infra margin. Enterprise-heavy mix pushes MRR past $180k at the same user count.</t>
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>• Rule of thumb: total team cost should stay below 50% of MRR at every milestone. First FTE breaks this rule intentionally — it's the classic S-curve dip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>• Never hire a FTE for something a fractional does &lt;20 hrs/week. Wait until the role is genuinely full-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>• Prefer converting a fractional to FTE only after 3+ months working together. That's the cheapest de-risked hire path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>• Every outsource line above has a SaaS or automation alternative — try that first for one quarter (Snyk instead of security consultant, GitHub Actions instead of DevOps).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>• Delay Security FTE until first enterprise deal is signed; before that, fractional + SaaS covers 90%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>• Emergent contract dev is functionally the cheapest fractional SWE on market — use it until $25k MRR before hiring FTE #1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,16 +176,22 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1614,10 +1620,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1628,408 +1634,864 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>30 / 60 / 90 / 180 Day Cash Flow (tech only)</t>
+          <t>30 / 60 / 90 / 180 Day Cash Flow — ALL-IN</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Assumes UK launch by day 60. Emergent contract devs sunset at day 120. Revenue = paid users × blended $70.60 ARPU.</t>
+          <t>Every $ that leaves the account: hard costs + AI + security + outsource + any FTEs. Assumes UK launch by day 60. Realistic user ramp 0→10→40→100. Revenue = paid users × $70.60 blended ARPU.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TEAM ROSTER IN THIS 180-DAY WINDOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Day 0–30</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Day 30–60</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Day 60–90</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Day 90–180 (mo avg)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>180-day total</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>TECH COSTS</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Day 90–180</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>1065</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1065</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>6830</v>
+          <t>2 founders (unpaid — sweat equity)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Not on P&amp;L</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Veryfi</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>550</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>700</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>3650</v>
+          <t>Emergent contract dev (fractional)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Taper</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sunset</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Sunsets month 5 as build stabilises</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Emergent LLM (dev credits)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>24000</v>
+          <t>Fractional QA engineer</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Starts at UK launch (day 60)</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Emergent contract developers</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Railway + Mongo + Redis</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>450</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>850</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Cloudflare + perimeter</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>330</v>
+          <t>FTE hires (any)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>None triggered — $25k MRR not hit in 180d</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Monitoring (Sentry paid + Datadog)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>220</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>830</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY COST BREAKDOWN</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Security tooling (Snyk, Doppler, MDM)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>1110</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Category / line</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Day 0–30</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Day 30–60</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Day 60–90</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Day 90–180 (mo avg)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>180-day total</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Core SaaS (Workspace, 1Password, GH)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>375</v>
-      </c>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>INFRA &amp; HARD COSTS</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr"/>
+      <c r="C14" s="23" t="inlineStr"/>
+      <c r="D14" s="23" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Backups (immutable + PITR)</t>
+          <t xml:space="preserve">  Plaid</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>20</v>
+        <v>1065</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>30</v>
+        <v>1065</v>
       </c>
       <c r="D15" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6830</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Veryfi OCR</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Railway + Mongo + Redis</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>850</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cloudflare + perimeter</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E18" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F18" s="6" t="n">
         <v>330</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL TECH COSTS / MO</t>
-        </is>
-      </c>
-      <c r="B16" s="15">
-        <f>SUM(B6:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="15">
-        <f>SUM(C6:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="15">
-        <f>SUM(D6:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="15">
-        <f>SUM(E6:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="15">
-        <f>SUM(F6:F15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Domain, Workspace, 1PW, GH</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Backups (immutable + PITR)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr"/>
+      <c r="C21" s="23" t="inlineStr"/>
+      <c r="D21" s="23" t="inlineStr"/>
+      <c r="E21" s="23" t="inlineStr"/>
+      <c r="F21" s="23" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Emergent LLM (dev credits)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>SECURITY TOOLING (SaaS)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr"/>
+      <c r="C23" s="23" t="inlineStr"/>
+      <c r="D23" s="23" t="inlineStr"/>
+      <c r="E23" s="23" t="inlineStr"/>
+      <c r="F23" s="23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Snyk / Doppler / MDM / EDR</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sentry + Datadog / monitoring</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>OUTSOURCE / FRACTIONAL</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr"/>
+      <c r="C26" s="23" t="inlineStr"/>
+      <c r="D26" s="23" t="inlineStr"/>
+      <c r="E26" s="23" t="inlineStr"/>
+      <c r="F26" s="23" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Emergent contract dev</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fractional QA engineer</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>FTE HIRES</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr"/>
+      <c r="C29" s="23" t="inlineStr"/>
+      <c r="D29" s="23" t="inlineStr"/>
+      <c r="E29" s="23" t="inlineStr"/>
+      <c r="F29" s="23" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (none triggered in first 180 days)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL COST / MONTH</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>SUM(B14:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="15">
+        <f>SUM(C14:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>SUM(D14:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="15">
+        <f>SUM(E14:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>SUM(F14:F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>Paid users (end of period)</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B34" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C34" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D34" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E34" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="F19" s="26" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>MRR (avg of period, $70.60 blended ARPU)</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n">
+      <c r="F34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Avg paid users in period</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="28">
-        <f>((B19+C19)/2)*70.60</f>
+      <c r="C35" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F35" s="25" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>MRR (avg users × $70.60)</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>353.0000000000001</v>
+      </c>
+      <c r="D36" s="28" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E36" s="28" t="n">
+        <v>4942.000000000001</v>
+      </c>
+      <c r="F36" s="28">
+        <f>B36+C36+D36+3*E36</f>
         <v/>
       </c>
-      <c r="D20" s="28">
-        <f>((C19+D19)/2)*70.60</f>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NET BURN (cost − revenue) /mo</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B31-B36</f>
         <v/>
       </c>
-      <c r="E20" s="28">
-        <f>((D19+E19)/2)*70.60</f>
+      <c r="C38" s="17">
+        <f>C31-C36</f>
         <v/>
       </c>
-      <c r="F20" s="28">
-        <f>C20+D20+3*E20</f>
+      <c r="D38" s="17">
+        <f>D31-D36</f>
         <v/>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NET BURN / MO (cost − revenue)</t>
-        </is>
-      </c>
-      <c r="B22" s="17">
-        <f>B16-B20</f>
+      <c r="E38" s="17">
+        <f>E31-E36</f>
         <v/>
       </c>
-      <c r="C22" s="17">
-        <f>C16-C20</f>
+      <c r="F38" s="17">
+        <f>F31-F36</f>
         <v/>
       </c>
-      <c r="D22" s="17">
-        <f>D16-D20</f>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>CUMULATIVE NET BURN (end of period)</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>B38</f>
         <v/>
       </c>
-      <c r="E22" s="17">
-        <f>E16-E20</f>
+      <c r="C39" s="15">
+        <f>B39+C38</f>
         <v/>
       </c>
-      <c r="F22" s="17">
-        <f>F16-F20</f>
+      <c r="D39" s="15">
+        <f>C39+D38</f>
         <v/>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Cash needed for 180 days</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <f>F22</f>
+      <c r="E39" s="15">
+        <f>D39+3*E38</f>
         <v/>
       </c>
+      <c r="F39" s="15">
+        <f>E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>CASH REQUIRED TO SURVIVE 180 DAYS</t>
+        </is>
+      </c>
+      <c r="B41" s="30">
+        <f>F39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>WHAT-IF LEVERS (edit assumptions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Impact on 180-day cash need</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Skip fractional QA until month 5</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>−$3,000</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Cut Emergent contract dev to $3k/mo from day 1</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>−$18,000</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Slows velocity ~40%</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Delay UK launch by 30 days (revenue starts month 4)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>+$1,800</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Loses UK market timing</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Pause LLM heavy-build &amp; use $500/mo baseline</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>−$25,500</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>You stop shipping AI features</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Hit 200 paying users by day 180 instead of 100</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>−$12,700</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Requires 2× conversion rate</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Emergent Studio prepay ($25k) covers LLM 4-5 months</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>−$0 (cash-neutral swap)</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Just changes timing</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2945,42 +3407,42 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>• 1 full-time engineer per ~$500k–$1M ARR in accounting SaaS (compliance overhead is real).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>• Never hire a full-time platform eng before 1,000 users — fractional or Cloudops does it cheaper.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>• Security engineer FTE only after first enterprise / SOC 2 Type II — before then, fractional + SaaS.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>• Rule of thumb: every tech FTE = base × 1.30 loaded (US) or × 1.15 (UK/EU via Deel).</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>• Prefer 1 senior remote FTE over 2 mid-level unless you already have a team lead.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>• Emergent contract dev is functionally the cheapest fractional SWE on the market — use it until $25k MRR.</t>
         </is>
@@ -3688,27 +4150,27 @@
           <t>Cost per paid user</t>
         </is>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="32">
         <f>C25/500</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="32">
         <f>D25/500</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="32">
         <f>E25/1500</f>
         <v/>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="32">
         <f>F25/1500</f>
         <v/>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="32">
         <f>G25/3000</f>
         <v/>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="32">
         <f>H25/3000</f>
         <v/>
       </c>
@@ -3797,13 +4259,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="24" t="n">
         <v>600</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="33" t="n">
         <v>0.0015</v>
       </c>
     </row>
@@ -3818,13 +4280,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="33" t="n">
         <v>0.0065</v>
       </c>
     </row>
@@ -3839,13 +4301,13 @@
           <t>Whisper</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="33" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -3860,13 +4322,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="33" t="n">
         <v>0.0008</v>
       </c>
     </row>
@@ -3881,13 +4343,13 @@
           <t>Claude Haiku 4.5</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="24" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="33" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3902,13 +4364,13 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>2000</v>
       </c>
-      <c r="E11" s="31" t="n">
+      <c r="E11" s="33" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3923,13 +4385,13 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="24" t="n">
         <v>15000</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="33" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -3944,13 +4406,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="24" t="n">
         <v>4000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>300</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E13" s="33" t="n">
         <v>0.006</v>
       </c>
     </row>
@@ -3965,13 +4427,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>800</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="33" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -3986,13 +4448,13 @@
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="33" t="n">
         <v>0.0009</v>
       </c>
     </row>
@@ -4007,13 +4469,13 @@
           <t>Gemini 3.5 Flash</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>200</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="33" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -4060,7 +4522,7 @@
       <c r="B21" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="24" t="n">
         <v>50</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -4079,7 +4541,7 @@
       <c r="B22" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="24" t="n">
         <v>800</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -4098,7 +4560,7 @@
       <c r="B23" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="24" t="n">
         <v>3500</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -4117,7 +4579,7 @@
       <c r="B24" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="24" t="n">
         <v>6000</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4136,7 +4598,7 @@
       <c r="B25" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -4155,7 +4617,7 @@
       <c r="B26" s="7" t="n">
         <v>0.02</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="24" t="n">
         <v>60000</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -5120,28 +5582,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>• Pre-launch = Day 1 essentials (Cloudflare, secrets, MFA, 1Password, encrypted backups).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>• 500-user tier layers in Snyk, MDM, EDR, basic SIEM — SOC 2 Type I readiness.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>• 1,500-user tier adds Vanta, pen-test, DAST, bug bounty.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>• 3,000+ = mature program (SIEM w/ retention, IR retainer, GitHub Advanced Security).</t>
         </is>
@@ -5940,13 +6402,13 @@
       <c r="B39" s="6" t="n">
         <v>2100</v>
       </c>
-      <c r="C39" s="25" t="n">
+      <c r="C39" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="25" t="n">
+      <c r="D39" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="E39" s="25" t="n">
+      <c r="E39" s="24" t="n">
         <v>22</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
@@ -5963,13 +6425,13 @@
       <c r="B40" s="6" t="n">
         <v>5500</v>
       </c>
-      <c r="C40" s="25" t="n">
+      <c r="C40" s="24" t="n">
         <v>78</v>
       </c>
-      <c r="D40" s="25" t="n">
+      <c r="D40" s="24" t="n">
         <v>73</v>
       </c>
-      <c r="E40" s="25" t="n">
+      <c r="E40" s="24" t="n">
         <v>58</v>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
@@ -5986,13 +6448,13 @@
       <c r="B41" s="6" t="n">
         <v>15500</v>
       </c>
-      <c r="C41" s="25" t="n">
+      <c r="C41" s="24" t="n">
         <v>220</v>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="24" t="n">
         <v>207</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="24" t="n">
         <v>163</v>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
@@ -6009,13 +6471,13 @@
       <c r="B42" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C42" s="25" t="n">
+      <c r="C42" s="24" t="n">
         <v>142</v>
       </c>
-      <c r="D42" s="25" t="n">
+      <c r="D42" s="24" t="n">
         <v>133</v>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="24" t="n">
         <v>105</v>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -6032,13 +6494,13 @@
       <c r="B43" s="6" t="n">
         <v>31750</v>
       </c>
-      <c r="C43" s="25" t="n">
+      <c r="C43" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="24" t="n">
         <v>423</v>
       </c>
-      <c r="E43" s="25" t="n">
+      <c r="E43" s="24" t="n">
         <v>334</v>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
@@ -6055,13 +6517,13 @@
       <c r="B44" s="6" t="n">
         <v>86083</v>
       </c>
-      <c r="C44" s="25" t="n">
+      <c r="C44" s="24" t="n">
         <v>1219</v>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="24" t="n">
         <v>1148</v>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="24" t="n">
         <v>906</v>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
@@ -6340,7 +6802,7 @@
           <t>Active today</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="24" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
@@ -6371,7 +6833,7 @@
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -6402,7 +6864,7 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="24" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -6477,7 +6939,7 @@
           <t>1,000 users</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="F13" s="6" t="n">
@@ -6508,7 +6970,7 @@
           <t>$25k MRR OR UK launch</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="24" t="n">
         <v>355</v>
       </c>
       <c r="F14" s="6" t="n">
@@ -6539,7 +7001,7 @@
           <t>SOC 2 kickoff / 1,000 users</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -6570,7 +7032,7 @@
           <t>SOC 2 Type I readiness (1,500u)</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="24" t="n">
         <v>1500</v>
       </c>
       <c r="F16" s="6" t="n">
@@ -6601,7 +7063,7 @@
           <t>1,500 users</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="24" t="n">
         <v>1500</v>
       </c>
       <c r="F17" s="6" t="n">
@@ -6632,7 +7094,7 @@
           <t>1,500 users OR SOC 2 Type II</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="24" t="n">
         <v>1500</v>
       </c>
       <c r="F18" s="6" t="n">
@@ -6707,7 +7169,7 @@
           <t>1,500 users</t>
         </is>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="24" t="n">
         <v>1500</v>
       </c>
       <c r="F23" s="6" t="n">
@@ -6738,7 +7200,7 @@
           <t>Marketing site + brand refresh</t>
         </is>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="F24" s="6" t="n">
@@ -6769,7 +7231,7 @@
           <t>1,500 users</t>
         </is>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="24" t="n">
         <v>1500</v>
       </c>
       <c r="F25" s="6" t="n">
@@ -6800,7 +7262,7 @@
           <t>3,000 users OR $60k MRR</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="24" t="n">
         <v>850</v>
       </c>
       <c r="F26" s="6" t="n">
@@ -6831,7 +7293,7 @@
           <t>SOC 2 Type II + first enterprise deal</t>
         </is>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="24" t="n">
         <v>3000</v>
       </c>
       <c r="F27" s="6" t="n">
@@ -6862,7 +7324,7 @@
           <t>3,000 users</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="24" t="n">
         <v>3000</v>
       </c>
       <c r="F28" s="6" t="n">
@@ -7115,42 +7577,42 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>• Rule of thumb: total team cost should stay below 50% of MRR at every milestone. First FTE breaks this rule intentionally — it's the classic S-curve dip.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>• Never hire a FTE for something a fractional does &lt;20 hrs/week. Wait until the role is genuinely full-time.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>• Prefer converting a fractional to FTE only after 3+ months working together. That's the cheapest de-risked hire path.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>• Every outsource line above has a SaaS or automation alternative — try that first for one quarter (Snyk instead of security consultant, GitHub Actions instead of DevOps).</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>• Delay Security FTE until first enterprise deal is signed; before that, fractional + SaaS covers 90%.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>• Emergent contract dev is functionally the cheapest fractional SWE on market — use it until $25k MRR before hiring FTE #1.</t>
         </is>

--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -16,6 +16,7 @@
     <sheet name="7. Security" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="8. Profit Breakdown" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="9. Hire Timeline" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. Exit Valuation" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,12 +25,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="$#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;×&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -134,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +201,25 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -968,6 +989,795 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exit Valuation — editable model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Edit the yellow cells to change users, growth rate, NRR, or multiples. Everything below re-computes live in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. EDITABLE INPUTS  (yellow cells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Total paid users at exit</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>Baseline plan target</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Blended ARPU ($/mo)</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>From Summary tab tier mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Monthly growth rate (MoM %)</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>8% MoM = healthy SaaS growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Net Revenue Retention (annual)</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>&gt;110% = premium; &lt;90% = discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Monthly logo churn</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>&gt;5% = downside multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Gross margin (all-in, at exit)</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>From Profit Breakdown tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>B. DERIVED METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>MRR at exit</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>ARR at exit</t>
+        </is>
+      </c>
+      <c r="B14" s="38">
+        <f>B13*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Annualised growth rate</t>
+        </is>
+      </c>
+      <c r="B15" s="39">
+        <f>(1+B7)^12-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Rule of 40 score (growth% + margin%)</t>
+        </is>
+      </c>
+      <c r="B16" s="40">
+        <f>((1+B7)^12-1)+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>C. VALUATION BY BUYER TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Buyer type</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>× ARR (low)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>× ARR (high)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Valuation (low)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Valuation (high)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Realistic mid</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Distressed / flat growth / high churn</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="43">
+        <f>B20*B14</f>
+        <v/>
+      </c>
+      <c r="E20" s="43">
+        <f>C20*B14</f>
+        <v/>
+      </c>
+      <c r="F20" s="43">
+        <f>(D20+E20)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>Bootstrapped roll-up (Constellation, Tiny, Valsoft)</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="43">
+        <f>B21*B14</f>
+        <v/>
+      </c>
+      <c r="E21" s="43">
+        <f>C21*B14</f>
+        <v/>
+      </c>
+      <c r="F21" s="43">
+        <f>(D21+E21)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>Vertical SaaS PE (Vista sub-scale tier)</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="43">
+        <f>B22*B14</f>
+        <v/>
+      </c>
+      <c r="E22" s="43">
+        <f>C22*B14</f>
+        <v/>
+      </c>
+      <c r="F22" s="43">
+        <f>(D22+E22)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>Strategic — accounting ecosystem (Intuit, Xero, Sage)</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="43">
+        <f>B23*B14</f>
+        <v/>
+      </c>
+      <c r="E23" s="43">
+        <f>C23*B14</f>
+        <v/>
+      </c>
+      <c r="F23" s="43">
+        <f>(D23+E23)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Strategic + AI premium (right buyer, right time)</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="43">
+        <f>B24*B14</f>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>C24*B14</f>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>(D24+E24)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>D. SENSITIVITY GRID — growth × NRR (uses 6× base multiple, then adjusts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Adjustment logic: base multiple = 6× ARR. Growth MoM adds ±0.5× per 2pp above/below 8%. NRR adds ±1× per 10pp above/below 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>MoM growth ↓  /  NRR →</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C29" s="44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D29" s="44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E29" s="44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F29" s="44" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B30" s="46">
+        <f>3.00*B14</f>
+        <v/>
+      </c>
+      <c r="C30" s="46">
+        <f>4.00*B14</f>
+        <v/>
+      </c>
+      <c r="D30" s="47">
+        <f>5.00*B14</f>
+        <v/>
+      </c>
+      <c r="E30" s="47">
+        <f>6.00*B14</f>
+        <v/>
+      </c>
+      <c r="F30" s="47">
+        <f>7.00*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B31" s="46">
+        <f>3.75*B14</f>
+        <v/>
+      </c>
+      <c r="C31" s="46">
+        <f>4.75*B14</f>
+        <v/>
+      </c>
+      <c r="D31" s="47">
+        <f>5.75*B14</f>
+        <v/>
+      </c>
+      <c r="E31" s="47">
+        <f>6.75*B14</f>
+        <v/>
+      </c>
+      <c r="F31" s="47">
+        <f>7.75*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B32" s="46">
+        <f>4.50*B14</f>
+        <v/>
+      </c>
+      <c r="C32" s="47">
+        <f>5.50*B14</f>
+        <v/>
+      </c>
+      <c r="D32" s="47">
+        <f>6.50*B14</f>
+        <v/>
+      </c>
+      <c r="E32" s="47">
+        <f>7.50*B14</f>
+        <v/>
+      </c>
+      <c r="F32" s="48">
+        <f>8.50*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B33" s="47">
+        <f>5.50*B14</f>
+        <v/>
+      </c>
+      <c r="C33" s="47">
+        <f>6.50*B14</f>
+        <v/>
+      </c>
+      <c r="D33" s="47">
+        <f>7.50*B14</f>
+        <v/>
+      </c>
+      <c r="E33" s="48">
+        <f>8.50*B14</f>
+        <v/>
+      </c>
+      <c r="F33" s="48">
+        <f>9.50*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="B34" s="47">
+        <f>7.00*B14</f>
+        <v/>
+      </c>
+      <c r="C34" s="48">
+        <f>8.00*B14</f>
+        <v/>
+      </c>
+      <c r="D34" s="48">
+        <f>9.00*B14</f>
+        <v/>
+      </c>
+      <c r="E34" s="48">
+        <f>10.00*B14</f>
+        <v/>
+      </c>
+      <c r="F34" s="48">
+        <f>11.00*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>E. LEVERS THAT MOVE YOU UP THE STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Multiple impact</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Effort / timing</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Grow 10%+ MoM in the 6 months before exit</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>+1-2× ARR</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Push growth marketing months 8-14</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Push NRR above 110% (expansion revenue)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>+1-2× ARR</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Add Enterprise upsells + usage-based add-ons</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Cut monthly churn under 3%</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>+0.5-1× ARR</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding + activation + CS ownership</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Land 1-2 marquee Partner (WL) accounts</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>+1× ARR</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Strategic story validates the platform</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Ship SOC 2 Type II before diligence</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>+0.5× ARR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Removes a diligence blocker; 6-9 mo lead</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Reach $5M+ ARR (institutional bar)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>+1× ARR</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Above $5M ARR the buyer pool 3× larger</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Prove AI IP is proprietary (own the model)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>+1-3× ARR</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Strategic AI-premium buyers only</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Have 2+ term sheets in parallel (competitive)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>+1-2× ARR</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Banker-run process at exit</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>F. HEADLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>Downside floor (2× ARR)</t>
+        </is>
+      </c>
+      <c r="B50" s="47">
+        <f>2*B14</f>
+        <v/>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>Flat growth, average churn, financial buyer only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>Base case (6-7× ARR)</t>
+        </is>
+      </c>
+      <c r="B51" s="47">
+        <f>6.5*B14</f>
+        <v/>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>8% MoM growth, ~105% NRR, PE or roll-up buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>Upside strategic (10× ARR)</t>
+        </is>
+      </c>
+      <c r="B52" s="47">
+        <f>10*B14</f>
+        <v/>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>Intuit/Xero threat model or AI IP premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>Best case competitive process (12× ARR)</t>
+        </is>
+      </c>
+      <c r="B53" s="47">
+        <f>12*B14</f>
+        <v/>
+      </c>
+      <c r="C53" s="35" t="inlineStr">
+        <is>
+          <t>Two term sheets + growth + NRR all firing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -599,7 +599,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SmartBooks — Tech-Only Cost Model (v5, Feb 2026)</t>
+          <t>Business Software — Tech-Only Cost Model (v5, Feb 2026)</t>
         </is>
       </c>
     </row>
@@ -610,6 +610,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -755,6 +756,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -836,6 +838,8 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -961,6 +965,8 @@
       </c>
       <c r="F25" s="5" t="inlineStr"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -971,7 +977,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>At 1,500 paid users on a blended $71 ARPU, SmartBooks runs ~$11k/mo of pure tech cost against ~$106k MRR — 90% gross margin on the infra layer. Today's pre-revenue burn is ~$15.5k/mo of which $12k is temporary build velocity that tapers by month 6.</t>
+          <t>At 1,500 paid users on a blended $71 ARPU, Business Software runs ~$11k/mo of pure tech cost against ~$106k MRR — 90% gross margin on the infra layer. Today's pre-revenue burn is ~$15.5k/mo of which $12k is temporary build velocity that tapers by month 6.</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1027,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1118,6 +1125,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1169,6 +1177,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -1334,6 +1343,8 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1495,6 +1506,8 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -1691,6 +1704,8 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
     </row>
+    <row r="47"/>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1807,6 +1822,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2069,6 +2085,7 @@
       <c r="C17" s="14" t="n"/>
       <c r="D17" s="14" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -2171,6 +2188,7 @@
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="16" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -2333,6 +2351,7 @@
       <c r="C34" s="18" t="n"/>
       <c r="D34" s="18" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
@@ -2346,6 +2365,7 @@
       <c r="C36" s="14" t="n"/>
       <c r="D36" s="14" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -2455,6 +2475,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2622,6 +2643,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -3012,6 +3035,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -3082,6 +3106,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
@@ -3136,6 +3161,7 @@
         <v/>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
@@ -3147,6 +3173,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
@@ -3338,6 +3365,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3569,6 +3597,8 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -3960,6 +3990,8 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -4209,6 +4241,8 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -4310,6 +4344,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4922,6 +4957,7 @@
         <v>150</v>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
@@ -5024,6 +5060,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5289,6 +5326,8 @@
         <v>0.003</v>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -5437,6 +5476,8 @@
         <v>70</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -5627,6 +5668,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -6359,6 +6401,7 @@
         <v>240</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -6391,6 +6434,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
         <is>
@@ -6466,6 +6510,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6687,6 +6732,8 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -6908,6 +6955,8 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -7165,6 +7214,8 @@
         <v>2651000.000000001</v>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -7341,6 +7392,8 @@
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
     </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -7495,6 +7548,8 @@
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
     </row>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
@@ -7549,6 +7604,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7686,6 +7742,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -7916,6 +7974,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -8146,6 +8206,8 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -8379,6 +8441,8 @@
         <v>0.2551935788479697</v>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>

--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>0.35</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>26.25</v>
+        <v>27.65</v>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>70.60000000000001</v>
+        <v>72</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>70.60000000000001</v>
+        <v>72</v>
       </c>
       <c r="F10" s="9" t="inlineStr"/>
     </row>
@@ -880,16 +880,16 @@
         <v>100</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>7060.000000000001</v>
+        <v>7200</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>3500</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3560.000000000001</v>
+        <v>3700</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.5042492917847026</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
     </row>
@@ -898,16 +898,16 @@
         <v>250</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>17650</v>
+        <v>18000</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>4500</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>13150</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.7450424929178471</v>
+        <v>0.75</v>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
     </row>
@@ -916,16 +916,16 @@
         <v>500</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>35300.00000000001</v>
+        <v>36000</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>4000</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>31300.00000000001</v>
+        <v>32000</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.886685552407932</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
     </row>
@@ -934,16 +934,16 @@
         <v>1500</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>11000</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>94900.00000000001</v>
+        <v>97000</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.8961284230406044</v>
+        <v>0.8981481481481481</v>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
     </row>
@@ -952,16 +952,16 @@
         <v>3000</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>26000</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>185800</v>
+        <v>190000</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.8772426817752597</v>
+        <v>0.8796296296296297</v>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
     </row>
@@ -977,7 +977,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>At 1,500 paid users on a blended $71 ARPU, Business Software runs ~$11k/mo of pure tech cost against ~$106k MRR — 90% gross margin on the infra layer. Today's pre-revenue burn is ~$15.5k/mo of which $12k is temporary build velocity that tapers by month 6.</t>
+          <t>At 1,500 paid users on a blended $72 ARPU, Business Software runs ~$11k/mo of pure tech cost against ~$106k MRR — 90% gross margin on the infra layer. Today's pre-revenue burn is ~$15.5k/mo of which $12k is temporary build velocity that tapers by month 6.</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every $ that leaves the account: hard costs + AI + security + outsource + any FTEs. Assumes UK launch by day 60. Realistic user ramp 0→10→40→100. Revenue = paid users × $70.60 blended ARPU.</t>
+          <t>Every $ that leaves the account: hard costs + AI + security + outsource + any FTEs. Assumes UK launch by day 60. Realistic user ramp 0→10→40→100. Revenue = paid users × $72.00 blended ARPU.</t>
         </is>
       </c>
     </row>
@@ -3086,20 +3086,20 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>MRR (avg users × $70.60)</t>
+          <t>MRR (avg users × $72.00)</t>
         </is>
       </c>
       <c r="B36" s="28" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="28" t="n">
-        <v>353.0000000000001</v>
+        <v>360</v>
       </c>
       <c r="D36" s="28" t="n">
-        <v>1765</v>
+        <v>1800</v>
       </c>
       <c r="E36" s="28" t="n">
-        <v>4942.000000000001</v>
+        <v>5040</v>
       </c>
       <c r="F36" s="28">
         <f>B36+C36+D36+3*E36</f>
@@ -5641,7 +5641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Annual pen-test (amortised /mo)</t>
+          <t>SOC 2 Type I auditor (one-time, amortised)</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
@@ -6302,13 +6302,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>750</v>
+        <v>1670</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1000</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="25">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>IR retainer (Kroll / Mandiant)</t>
+          <t>SOC 2 Type II auditor (annual, amortised)</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -6335,51 +6335,51 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>400</v>
+        <v>2100</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>800</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Fraud / Abuse</t>
+          <t>Compliance Ops</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>reCAPTCHA Enterprise + IP intel</t>
+          <t>Annual pen-test (amortised /mo)</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Fraud / Abuse</t>
+          <t>Compliance Ops</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Rate-limit + abuse mgmt (Kong/Cloudflare)</t>
+          <t>IR retainer (Kroll / Mandiant)</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -6389,87 +6389,147 @@
         <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Fraud / Abuse</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>reCAPTCHA Enterprise + IP intel</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Fraud / Abuse</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Rate-limit + abuse mgmt (Kong/Cloudflare)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H29" s="6" t="n">
         <v>240</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL SECURITY / MONTH</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="15">
-        <f>SUM(C5:C27)</f>
-        <v/>
-      </c>
-      <c r="D29" s="15">
-        <f>SUM(D5:D27)</f>
-        <v/>
-      </c>
-      <c r="E29" s="15">
-        <f>SUM(E5:E27)</f>
-        <v/>
-      </c>
-      <c r="F29" s="15">
-        <f>SUM(F5:F27)</f>
-        <v/>
-      </c>
-      <c r="G29" s="15">
-        <f>SUM(G5:G27)</f>
-        <v/>
-      </c>
-      <c r="H29" s="15">
-        <f>SUM(H5:H27)</f>
-        <v/>
       </c>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>• Pre-launch = Day 1 essentials (Cloudflare, secrets, MFA, 1Password, encrypted backups).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>• 500-user tier layers in Snyk, MDM, EDR, basic SIEM — SOC 2 Type I readiness.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL SECURITY / MONTH</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="15">
+        <f>SUM(C5:C29)</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>SUM(D5:D29)</f>
+        <v/>
+      </c>
+      <c r="E31" s="15">
+        <f>SUM(E5:E29)</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>SUM(F5:F29)</f>
+        <v/>
+      </c>
+      <c r="G31" s="15">
+        <f>SUM(G5:G29)</f>
+        <v/>
+      </c>
+      <c r="H31" s="15">
+        <f>SUM(H5:H29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t>• 1,500-user tier adds Vanta, pen-test, DAST, bug bounty.</t>
+          <t>• Pre-launch = Day 1 essentials (Cloudflare, secrets, MFA, 1Password, encrypted backups).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
         <is>
+          <t>• 500-user tier layers in Snyk, MDM, EDR, basic SIEM — SOC 2 Type I readiness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>• 1,500-user tier adds Vanta, pen-test, DAST, bug bounty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
           <t>• 3,000+ = mature program (SIEM w/ retention, IR retainer, GitHub Advanced Security).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6506,7 +6566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blended ARPU = $70.60 (40/35/15/10 mix of $38/$75/$95/$149). All-in adds outsource + FTE loaded costs.</t>
+          <t>Blended ARPU = $72.00 (40/35/15/10 mix of $38/$79/$95/$149). All-in adds outsource + FTE loaded costs.</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6591,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Standard $75 (35%)</t>
+          <t>Standard $79 (35%)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -6565,7 +6625,7 @@
         <v>1520</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2625</v>
+        <v>2765</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1425</v>
@@ -6574,10 +6634,10 @@
         <v>1490</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7060</v>
+        <v>7200</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>84720</v>
+        <v>86400</v>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -6590,7 +6650,7 @@
         <v>3800</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6562.5</v>
+        <v>6912.5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>3562.5</v>
@@ -6599,10 +6659,10 @@
         <v>3725</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17650</v>
+        <v>18000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
@@ -6615,7 +6675,7 @@
         <v>7600</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>13125</v>
+        <v>13825</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>7125</v>
@@ -6624,10 +6684,10 @@
         <v>7450</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>35300</v>
+        <v>36000</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>423600</v>
+        <v>432000</v>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
@@ -6640,7 +6700,7 @@
         <v>15200</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>26250</v>
+        <v>27650</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>14250</v>
@@ -6649,10 +6709,10 @@
         <v>14900</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>70600</v>
+        <v>72000</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>847200</v>
+        <v>864000</v>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -6665,7 +6725,7 @@
         <v>22800</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>39375</v>
+        <v>41475</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>21375</v>
@@ -6674,10 +6734,10 @@
         <v>22350</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1270800</v>
+        <v>1296000</v>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -6690,7 +6750,7 @@
         <v>45600</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>78750</v>
+        <v>82950</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>42750</v>
@@ -6699,10 +6759,10 @@
         <v>44700</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2541600</v>
+        <v>2592000</v>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -6715,7 +6775,7 @@
         <v>76000</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>131250</v>
+        <v>138250</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>71250</v>
@@ -6724,10 +6784,10 @@
         <v>74500</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>353000</v>
+        <v>360000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4236000</v>
+        <v>4320000</v>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -6785,19 +6845,19 @@
         <v>100</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7060.000000000001</v>
+        <v>7200</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>3500</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3560.000000000001</v>
+        <v>3700</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.5042492917847026</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>42720.00000000001</v>
+        <v>44400</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>35</v>
@@ -6810,19 +6870,19 @@
         <v>250</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>17650</v>
+        <v>18000</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>4000</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13650</v>
+        <v>14000</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.773371104815864</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>163800.0000000001</v>
+        <v>168000</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>16</v>
@@ -6835,19 +6895,19 @@
         <v>500</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>35300.00000000001</v>
+        <v>36000</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>4000</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>31300.00000000001</v>
+        <v>32000</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.886685552407932</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>375600.0000000001</v>
+        <v>384000</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>8</v>
@@ -6860,19 +6920,19 @@
         <v>1000</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>70600.00000000001</v>
+        <v>72000</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>8500</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>62100.00000000001</v>
+        <v>63500</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.8796033994334278</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>745200.0000000002</v>
+        <v>762000</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>8.5</v>
@@ -6885,19 +6945,19 @@
         <v>1500</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>11000</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>94900.00000000001</v>
+        <v>97000</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.8961284230406044</v>
+        <v>0.8981481481481481</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1138800</v>
+        <v>1164000</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>7.333333333333333</v>
@@ -6910,19 +6970,19 @@
         <v>3000</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>26000</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>185800</v>
+        <v>190000</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.8772426817752597</v>
+        <v>0.8796296296296297</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2229600</v>
+        <v>2280000</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>8.666666666666666</v>
@@ -6935,19 +6995,19 @@
         <v>5000</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>353000.0000000001</v>
+        <v>360000</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>42000</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>311000.0000000001</v>
+        <v>318000</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.8810198300283286</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3732000.000000001</v>
+        <v>3816000</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>8.4</v>
@@ -7016,7 +7076,7 @@
         <v>100</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>7060.000000000001</v>
+        <v>7200</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>3500</v>
@@ -7031,13 +7091,13 @@
         <v>6500</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>560.0000000000009</v>
+        <v>700</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>0.07932011331444772</v>
+        <v>0.09722222222222222</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>6720.000000000011</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="29">
@@ -7045,7 +7105,7 @@
         <v>250</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>17650</v>
+        <v>18000</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>4000</v>
@@ -7060,13 +7120,13 @@
         <v>8000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>9650.000000000004</v>
+        <v>10000</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0.5467422096317281</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>115800</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="30">
@@ -7074,7 +7134,7 @@
         <v>500</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>35300.00000000001</v>
+        <v>36000</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>4000</v>
@@ -7089,13 +7149,13 @@
         <v>10000</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>25300.00000000001</v>
+        <v>26000</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0.7167138810198301</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>303600.0000000001</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="31">
@@ -7103,7 +7163,7 @@
         <v>1000</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>70600.00000000001</v>
+        <v>72000</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>8500</v>
@@ -7118,13 +7178,13 @@
         <v>31750</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>38850.00000000001</v>
+        <v>40250</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0.5502832861189803</v>
+        <v>0.5590277777777778</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>466200.0000000002</v>
+        <v>483000</v>
       </c>
     </row>
     <row r="32">
@@ -7132,7 +7192,7 @@
         <v>1500</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>11000</v>
@@ -7147,13 +7207,13 @@
         <v>53750</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>52150.00000000001</v>
+        <v>54250</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0.4924457034938622</v>
+        <v>0.5023148148148148</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>625800.0000000002</v>
+        <v>651000</v>
       </c>
     </row>
     <row r="33">
@@ -7161,7 +7221,7 @@
         <v>3000</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>26000</v>
@@ -7176,13 +7236,13 @@
         <v>118083.3333333333</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>93716.6666666667</v>
+        <v>97916.66666666667</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0.4424771797293044</v>
+        <v>0.4533179012345679</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1124600</v>
+        <v>1175000</v>
       </c>
     </row>
     <row r="34">
@@ -7190,7 +7250,7 @@
         <v>5000</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>353000.0000000001</v>
+        <v>360000</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>42000</v>
@@ -7205,13 +7265,13 @@
         <v>132083.3333333333</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>220916.6666666667</v>
+        <v>227916.6666666667</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0.625826251180359</v>
+        <v>0.6331018518518519</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2651000.000000001</v>
+        <v>2735000</v>
       </c>
     </row>
     <row r="35"/>
@@ -7241,7 +7301,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>@ $75 Std</t>
+          <t>@ $79 Std</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -7264,10 +7324,10 @@
         <v>2100</v>
       </c>
       <c r="C39" s="24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" s="24" t="n">
         <v>22</v>
@@ -7287,10 +7347,10 @@
         <v>5500</v>
       </c>
       <c r="C40" s="24" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E40" s="24" t="n">
         <v>58</v>
@@ -7310,10 +7370,10 @@
         <v>15500</v>
       </c>
       <c r="C41" s="24" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D41" s="24" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E41" s="24" t="n">
         <v>163</v>
@@ -7333,10 +7393,10 @@
         <v>10000</v>
       </c>
       <c r="C42" s="24" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D42" s="24" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E42" s="24" t="n">
         <v>105</v>
@@ -7356,10 +7416,10 @@
         <v>31750</v>
       </c>
       <c r="C43" s="24" t="n">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D43" s="24" t="n">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="E43" s="24" t="n">
         <v>334</v>
@@ -7379,10 +7439,10 @@
         <v>86083</v>
       </c>
       <c r="C44" s="24" t="n">
-        <v>1219</v>
+        <v>1196</v>
       </c>
       <c r="D44" s="24" t="n">
-        <v>1148</v>
+        <v>1090</v>
       </c>
       <c r="E44" s="24" t="n">
         <v>906</v>
@@ -7459,10 +7519,10 @@
         <v>0.02</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>55.88</v>
+        <v>57.08</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>83820</v>
+        <v>85620</v>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
@@ -7486,10 +7546,10 @@
         <v>0.1</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>70.60000000000001</v>
+        <v>72</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
@@ -7513,10 +7573,10 @@
         <v>0.25</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>91.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>136650</v>
+        <v>138450</v>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
@@ -7540,10 +7600,10 @@
         <v>0.35</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>103.2</v>
+        <v>104.2</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>154800</v>
+        <v>156300</v>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -8273,10 +8333,10 @@
         <v>3000</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>7060.000000000001</v>
+        <v>7200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.4249291784702549</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -8300,10 +8360,10 @@
         <v>4000</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>17650</v>
+        <v>18000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.2266288951841359</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="35">
@@ -8327,10 +8387,10 @@
         <v>6000</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>35300.00000000001</v>
+        <v>36000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.169971671388102</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -8354,10 +8414,10 @@
         <v>23250</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>70600.00000000001</v>
+        <v>72000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.3293201133144475</v>
+        <v>0.3229166666666667</v>
       </c>
     </row>
     <row r="37">
@@ -8381,10 +8441,10 @@
         <v>42750</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>105900</v>
+        <v>108000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.4036827195467422</v>
+        <v>0.3958333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -8408,10 +8468,10 @@
         <v>92083.33333333333</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>211800</v>
+        <v>216000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.4347655020459552</v>
+        <v>0.4263117283950617</v>
       </c>
     </row>
     <row r="39">
@@ -8435,10 +8495,10 @@
         <v>90083.33333333333</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>353000.0000000001</v>
+        <v>360000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.2551935788479697</v>
+        <v>0.2502314814814814</v>
       </c>
     </row>
     <row r="40"/>

--- a/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
+++ b/frontend/public/downloads/SmartBooks_Cost_Model.xlsx
@@ -17,6 +17,7 @@
     <sheet name="8. Profit Breakdown" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="9. Hire Timeline" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="10. Exit Valuation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11. Practice Partner" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,6 +221,11 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1793,6 +1799,1013 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Practice Partner — accountant wholesale program</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>$349/mo firm license + $15/client seat + white-label. Affiliate commission $125/mo/firm. Yellow cells are editable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. EDITABLE INPUTS (yellow cells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Firm license price /mo</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Firm license annual (prepaid)</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Per-client seat price /mo</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Accountant's $/client charged</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Affiliate commission /mo/firm</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Our COGS per client seat</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>B. ACCOUNTANT P&amp;L — profit at different client counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Firm license</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Seat fees</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Client revenue</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Net profit /mo</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C14" s="43">
+        <f>5*B7</f>
+        <v/>
+      </c>
+      <c r="D14" s="43">
+        <f>B5+(5*B7)</f>
+        <v/>
+      </c>
+      <c r="E14" s="43">
+        <f>5*B8</f>
+        <v/>
+      </c>
+      <c r="F14" s="51">
+        <f>E14-D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="43">
+        <f>F14*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C15" s="43">
+        <f>10*B7</f>
+        <v/>
+      </c>
+      <c r="D15" s="43">
+        <f>B5+(10*B7)</f>
+        <v/>
+      </c>
+      <c r="E15" s="43">
+        <f>10*B8</f>
+        <v/>
+      </c>
+      <c r="F15" s="52">
+        <f>E15-D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="43">
+        <f>F15*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C16" s="43">
+        <f>20*B7</f>
+        <v/>
+      </c>
+      <c r="D16" s="43">
+        <f>B5+(20*B7)</f>
+        <v/>
+      </c>
+      <c r="E16" s="43">
+        <f>20*B8</f>
+        <v/>
+      </c>
+      <c r="F16" s="52">
+        <f>E16-D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="43">
+        <f>F16*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="B17" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C17" s="43">
+        <f>30*B7</f>
+        <v/>
+      </c>
+      <c r="D17" s="43">
+        <f>B5+(30*B7)</f>
+        <v/>
+      </c>
+      <c r="E17" s="43">
+        <f>30*B8</f>
+        <v/>
+      </c>
+      <c r="F17" s="53">
+        <f>E17-D17</f>
+        <v/>
+      </c>
+      <c r="G17" s="43">
+        <f>F17*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B18" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C18" s="43">
+        <f>50*B7</f>
+        <v/>
+      </c>
+      <c r="D18" s="43">
+        <f>B5+(50*B7)</f>
+        <v/>
+      </c>
+      <c r="E18" s="43">
+        <f>50*B8</f>
+        <v/>
+      </c>
+      <c r="F18" s="53">
+        <f>E18-D18</f>
+        <v/>
+      </c>
+      <c r="G18" s="43">
+        <f>F18*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="50" t="n">
+        <v>75</v>
+      </c>
+      <c r="B19" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C19" s="43">
+        <f>75*B7</f>
+        <v/>
+      </c>
+      <c r="D19" s="43">
+        <f>B5+(75*B7)</f>
+        <v/>
+      </c>
+      <c r="E19" s="43">
+        <f>75*B8</f>
+        <v/>
+      </c>
+      <c r="F19" s="53">
+        <f>E19-D19</f>
+        <v/>
+      </c>
+      <c r="G19" s="43">
+        <f>F19*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C20" s="43">
+        <f>100*B7</f>
+        <v/>
+      </c>
+      <c r="D20" s="43">
+        <f>B5+(100*B7)</f>
+        <v/>
+      </c>
+      <c r="E20" s="43">
+        <f>100*B8</f>
+        <v/>
+      </c>
+      <c r="F20" s="53">
+        <f>E20-D20</f>
+        <v/>
+      </c>
+      <c r="G20" s="43">
+        <f>F20*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="B21" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C21" s="43">
+        <f>150*B7</f>
+        <v/>
+      </c>
+      <c r="D21" s="43">
+        <f>B5+(150*B7)</f>
+        <v/>
+      </c>
+      <c r="E21" s="43">
+        <f>150*B8</f>
+        <v/>
+      </c>
+      <c r="F21" s="53">
+        <f>E21-D21</f>
+        <v/>
+      </c>
+      <c r="G21" s="43">
+        <f>F21*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="B22" s="43">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C22" s="43">
+        <f>200*B7</f>
+        <v/>
+      </c>
+      <c r="D22" s="43">
+        <f>B5+(200*B7)</f>
+        <v/>
+      </c>
+      <c r="E22" s="43">
+        <f>200*B8</f>
+        <v/>
+      </c>
+      <c r="F22" s="53">
+        <f>E22-D22</f>
+        <v/>
+      </c>
+      <c r="G22" s="43">
+        <f>F22*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>C. BUSINESS SOFTWARE P&amp;L — margin per Practice Partner firm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Clients in firm</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Total MRR from firm</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate payout</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Our COGS</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Net /mo</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="43">
+        <f>B5+(10*B7)</f>
+        <v/>
+      </c>
+      <c r="C26" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D26" s="43">
+        <f>10*B10</f>
+        <v/>
+      </c>
+      <c r="E26" s="53">
+        <f>B26-C26-D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="43">
+        <f>E26*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="B27" s="43">
+        <f>B5+(30*B7)</f>
+        <v/>
+      </c>
+      <c r="C27" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D27" s="43">
+        <f>30*B10</f>
+        <v/>
+      </c>
+      <c r="E27" s="53">
+        <f>B27-C27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="43">
+        <f>E27*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B28" s="43">
+        <f>B5+(50*B7)</f>
+        <v/>
+      </c>
+      <c r="C28" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D28" s="43">
+        <f>50*B10</f>
+        <v/>
+      </c>
+      <c r="E28" s="53">
+        <f>B28-C28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="43">
+        <f>E28*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="n">
+        <v>75</v>
+      </c>
+      <c r="B29" s="43">
+        <f>B5+(75*B7)</f>
+        <v/>
+      </c>
+      <c r="C29" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D29" s="43">
+        <f>75*B10</f>
+        <v/>
+      </c>
+      <c r="E29" s="53">
+        <f>B29-C29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="43">
+        <f>E29*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="B30" s="43">
+        <f>B5+(100*B7)</f>
+        <v/>
+      </c>
+      <c r="C30" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D30" s="43">
+        <f>100*B10</f>
+        <v/>
+      </c>
+      <c r="E30" s="53">
+        <f>B30-C30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="43">
+        <f>E30*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="B31" s="43">
+        <f>B5+(150*B7)</f>
+        <v/>
+      </c>
+      <c r="C31" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D31" s="43">
+        <f>150*B10</f>
+        <v/>
+      </c>
+      <c r="E31" s="53">
+        <f>B31-C31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="43">
+        <f>E31*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="B32" s="43">
+        <f>B5+(200*B7)</f>
+        <v/>
+      </c>
+      <c r="C32" s="43">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D32" s="43">
+        <f>200*B10</f>
+        <v/>
+      </c>
+      <c r="E32" s="53">
+        <f>B32-C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="43">
+        <f>E32*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>D. PORTFOLIO SCALE — Total revenue by # of Partner firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Firms in program</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Avg clients / firm</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Total client seats</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Total MRR</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Total ARR</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Our net /mo</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Our net /yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="50" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="D36" s="43">
+        <f>25*(B5+20*B7)</f>
+        <v/>
+      </c>
+      <c r="E36" s="43">
+        <f>D36*12</f>
+        <v/>
+      </c>
+      <c r="F36" s="43">
+        <f>D36-25*(B9+20*B10)</f>
+        <v/>
+      </c>
+      <c r="G36" s="52">
+        <f>F36*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B37" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D37" s="43">
+        <f>50*(B5+30*B7)</f>
+        <v/>
+      </c>
+      <c r="E37" s="43">
+        <f>D37*12</f>
+        <v/>
+      </c>
+      <c r="F37" s="43">
+        <f>D37-50*(B9+30*B10)</f>
+        <v/>
+      </c>
+      <c r="G37" s="52">
+        <f>F37*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="B38" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" s="50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D38" s="43">
+        <f>100*(B5+30*B7)</f>
+        <v/>
+      </c>
+      <c r="E38" s="43">
+        <f>D38*12</f>
+        <v/>
+      </c>
+      <c r="F38" s="43">
+        <f>D38-100*(B9+30*B10)</f>
+        <v/>
+      </c>
+      <c r="G38" s="52">
+        <f>F38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="50" t="n">
+        <v>250</v>
+      </c>
+      <c r="B39" s="50" t="n">
+        <v>40</v>
+      </c>
+      <c r="C39" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D39" s="43">
+        <f>250*(B5+40*B7)</f>
+        <v/>
+      </c>
+      <c r="E39" s="43">
+        <f>D39*12</f>
+        <v/>
+      </c>
+      <c r="F39" s="43">
+        <f>D39-250*(B9+40*B10)</f>
+        <v/>
+      </c>
+      <c r="G39" s="52">
+        <f>F39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="50" t="n">
+        <v>500</v>
+      </c>
+      <c r="B40" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C40" s="50" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D40" s="43">
+        <f>500*(B5+50*B7)</f>
+        <v/>
+      </c>
+      <c r="E40" s="43">
+        <f>D40*12</f>
+        <v/>
+      </c>
+      <c r="F40" s="43">
+        <f>D40-500*(B9+50*B10)</f>
+        <v/>
+      </c>
+      <c r="G40" s="52">
+        <f>F40*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B41" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C41" s="50" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D41" s="43">
+        <f>1000*(B5+50*B7)</f>
+        <v/>
+      </c>
+      <c r="E41" s="43">
+        <f>D41*12</f>
+        <v/>
+      </c>
+      <c r="F41" s="43">
+        <f>D41-1000*(B9+50*B10)</f>
+        <v/>
+      </c>
+      <c r="G41" s="52">
+        <f>F41*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>E. AFFILIATE INCOME — for referrers</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Firms referred</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Monthly income</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Annual income</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="43">
+        <f>5*B9</f>
+        <v/>
+      </c>
+      <c r="C45" s="43">
+        <f>B45*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B46" s="43">
+        <f>10*B9</f>
+        <v/>
+      </c>
+      <c r="C46" s="43">
+        <f>B46*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B47" s="43">
+        <f>20*B9</f>
+        <v/>
+      </c>
+      <c r="C47" s="43">
+        <f>B47*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B48" s="43">
+        <f>50*B9</f>
+        <v/>
+      </c>
+      <c r="C48" s="43">
+        <f>B48*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="B49" s="43">
+        <f>100*B9</f>
+        <v/>
+      </c>
+      <c r="C49" s="43">
+        <f>B49*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="B50" s="43">
+        <f>200*B9</f>
+        <v/>
+      </c>
+      <c r="C50" s="43">
+        <f>B50*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>F. KEY TAKEAWAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>• Accountant break-even: ~10 clients at $50/client. Every additional client = ~$35 pure margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>• Business Software makes 7× more per firm ($1,099 at 50 clients) than a regular Enterprise seat ($149).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>• At 500 Practice Partners × 50 clients each, this channel alone drives $6.6M ARR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
+        <is>
+          <t>• Affiliate at 20 firms referred = $2,500/mo recurring, lifetime. This is a real career for CPA newsletter operators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>• Annual prepay ($3,700) saves accountant $488/yr AND locks retention — worth pushing hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>• Our COGS assumption ($8/client) is conservative — real cost closer to $5-6/client at scale.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A43:G43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
